--- a/price-extension/price-template.xlsx
+++ b/price-extension/price-template.xlsx
@@ -7,13 +7,15 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="게시물" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구간별 여론" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주별 추이" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="댓글" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구간별 여론" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주별 추이" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'게시물'!$B$3:$Q$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'구간별 여론'!$B$5:$U$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'주별 추이'!$B$3:$N$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'댓글'!$B$3:$Q$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'구간별 여론'!$B$5:$AC$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'주별 추이'!$B$3:$Q$4</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -155,7 +157,7 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -219,6 +221,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -245,7 +250,7 @@
     <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="2" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
     <dxf>
       <font>
         <b val="1"/>
@@ -262,6 +267,17 @@
       <font>
         <b val="1"/>
         <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFE00000"/>
       </font>
     </dxf>
   </dxfs>
@@ -823,6 +839,9 @@
     <cfRule type="expression" priority="3" dxfId="2">
       <formula>L4="중립"</formula>
     </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>L4="단순비난"</formula>
+    </cfRule>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId1"/>
@@ -845,7 +864,174 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:U6"/>
+  <dimension ref="B3:Q4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5.5" customWidth="1" style="6" min="2" max="2"/>
+    <col width="16" customWidth="1" style="6" min="3" max="3"/>
+    <col width="8" customWidth="1" style="6" min="4" max="4"/>
+    <col width="34" customWidth="1" style="6" min="5" max="5"/>
+    <col width="34" customWidth="1" style="6" min="6" max="6"/>
+    <col width="20" customWidth="1" style="6" min="7" max="7"/>
+    <col width="17.7" customWidth="1" style="6" min="8" max="8"/>
+    <col width="14" customWidth="1" style="6" min="9" max="9"/>
+    <col width="7" customWidth="1" style="6" min="10" max="10"/>
+    <col width="60" customWidth="1" style="6" min="11" max="11"/>
+    <col width="8" customWidth="1" style="6" min="12" max="12"/>
+    <col width="10" customWidth="1" style="6" min="13" max="13"/>
+    <col width="22" customWidth="1" style="6" min="14" max="14"/>
+    <col width="22" customWidth="1" style="6" min="15" max="15"/>
+    <col width="10" customWidth="1" style="6" min="16" max="16"/>
+    <col width="40" customWidth="1" style="6" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="3">
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>동호회명</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>게시글 순번</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>게시글 제목</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>게시글 URL</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>구간</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>댓글 작성일</t>
+        </is>
+      </c>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>작성자 닉네임</t>
+        </is>
+      </c>
+      <c r="J3" s="16" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="K3" s="16" t="inlineStr">
+        <is>
+          <t>댓글 내용</t>
+        </is>
+      </c>
+      <c r="L3" s="16" t="inlineStr">
+        <is>
+          <t>가격 관련</t>
+        </is>
+      </c>
+      <c r="M3" s="16" t="inlineStr">
+        <is>
+          <t>댓글 여론</t>
+        </is>
+      </c>
+      <c r="N3" s="16" t="inlineStr">
+        <is>
+          <t>금액 언급</t>
+        </is>
+      </c>
+      <c r="O3" s="16" t="inlineStr">
+        <is>
+          <t>인상액 언급</t>
+        </is>
+      </c>
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t>인상액(만 원)</t>
+        </is>
+      </c>
+      <c r="Q3" s="16" t="inlineStr">
+        <is>
+          <t>요지</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>https://cafe.naver.com/</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="23" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="11" t="n"/>
+      <c r="L4" s="8" t="n"/>
+      <c r="M4" s="8" t="n"/>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="11" t="n"/>
+      <c r="P4" s="22" t="n"/>
+      <c r="Q4" s="11" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="B3:Q4"/>
+  <conditionalFormatting sqref="M4:M50000">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>M4="부정"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>M4="긍정"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>M4="중립"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="3">
+      <formula>M4="단순비난"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4:K50000 N4:P50000">
+    <cfRule type="expression" priority="5" dxfId="4">
+      <formula>OR($N4&lt;&gt;"",$O4&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;L&amp;"Aptos"&amp;10 &amp;K000000_x000d_# 본 문서는 현대자동차·기아의 정보자산으로 귀사와의 비밀유지계약 및 제반법률에 따라 법적 보호를 받습니다.</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="6" min="2" max="2"/>
@@ -867,25 +1053,33 @@
     <col width="11" customWidth="1" style="6" min="18" max="18"/>
     <col width="11" customWidth="1" style="6" min="19" max="19"/>
     <col width="11" customWidth="1" style="6" min="20" max="20"/>
-    <col width="70" customWidth="1" style="6" min="21" max="21"/>
+    <col width="11" customWidth="1" style="6" min="21" max="21"/>
+    <col width="8" customWidth="1" style="6" min="22" max="22"/>
+    <col width="8" customWidth="1" style="6" min="23" max="23"/>
+    <col width="8" customWidth="1" style="6" min="24" max="24"/>
+    <col width="9" customWidth="1" style="6" min="25" max="25"/>
+    <col width="11" customWidth="1" style="6" min="26" max="26"/>
+    <col width="10" customWidth="1" style="6" min="27" max="27"/>
+    <col width="12" customWidth="1" style="6" min="28" max="28"/>
+    <col width="70" customWidth="1" style="6" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="23" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>싼타페 F/L 예상 가격 여론 변화 (기준 사건 전후)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>{{conditions}}</t>
         </is>
       </c>
     </row>
     <row r="3" ht="150" customHeight="1" s="6">
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>{{overall}}</t>
         </is>
@@ -988,6 +1182,46 @@
         </is>
       </c>
       <c r="U5" s="16" t="inlineStr">
+        <is>
+          <t>가격 관련 댓글 수</t>
+        </is>
+      </c>
+      <c r="V5" s="16" t="inlineStr">
+        <is>
+          <t>댓글 긍정</t>
+        </is>
+      </c>
+      <c r="W5" s="16" t="inlineStr">
+        <is>
+          <t>댓글 중립</t>
+        </is>
+      </c>
+      <c r="X5" s="16" t="inlineStr">
+        <is>
+          <t>댓글 부정</t>
+        </is>
+      </c>
+      <c r="Y5" s="16" t="inlineStr">
+        <is>
+          <t>댓글 단순비난</t>
+        </is>
+      </c>
+      <c r="Z5" s="16" t="inlineStr">
+        <is>
+          <t>댓글 부정·비난 비율</t>
+        </is>
+      </c>
+      <c r="AA5" s="16" t="inlineStr">
+        <is>
+          <t>댓글 금액 언급</t>
+        </is>
+      </c>
+      <c r="AB5" s="16" t="inlineStr">
+        <is>
+          <t>댓글 인상액 평균(만 원)</t>
+        </is>
+      </c>
+      <c r="AC5" s="16" t="inlineStr">
         <is>
           <t>여론 요지</t>
         </is>
@@ -998,12 +1232,12 @@
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="22" t="n"/>
       <c r="E6" s="22" t="n"/>
-      <c r="F6" s="26" t="n"/>
+      <c r="F6" s="27" t="n"/>
       <c r="G6" s="22" t="n"/>
       <c r="H6" s="22" t="n"/>
       <c r="I6" s="22" t="n"/>
-      <c r="J6" s="27" t="n"/>
-      <c r="K6" s="27" t="n"/>
+      <c r="J6" s="28" t="n"/>
+      <c r="K6" s="28" t="n"/>
       <c r="L6" s="22" t="n"/>
       <c r="M6" s="22" t="n"/>
       <c r="N6" s="22" t="n"/>
@@ -1012,13 +1246,21 @@
       <c r="Q6" s="22" t="n"/>
       <c r="R6" s="22" t="n"/>
       <c r="S6" s="22" t="n"/>
-      <c r="T6" s="28" t="n"/>
-      <c r="U6" s="11" t="n"/>
+      <c r="T6" s="29" t="n"/>
+      <c r="U6" s="22" t="n"/>
+      <c r="V6" s="22" t="n"/>
+      <c r="W6" s="22" t="n"/>
+      <c r="X6" s="22" t="n"/>
+      <c r="Y6" s="22" t="n"/>
+      <c r="Z6" s="28" t="n"/>
+      <c r="AA6" s="22" t="n"/>
+      <c r="AB6" s="22" t="n"/>
+      <c r="AC6" s="11" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="B5:U6"/>
+  <autoFilter ref="B5:AC6"/>
   <mergeCells count="1">
-    <mergeCell ref="B3:U3"/>
+    <mergeCell ref="B3:AC3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
@@ -1032,13 +1274,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:N4"/>
+  <dimension ref="B1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" style="6" min="2" max="2"/>
@@ -1054,17 +1296,20 @@
     <col width="11" customWidth="1" style="6" min="12" max="12"/>
     <col width="11" customWidth="1" style="6" min="13" max="13"/>
     <col width="11" customWidth="1" style="6" min="14" max="14"/>
+    <col width="11" customWidth="1" style="6" min="15" max="15"/>
+    <col width="11" customWidth="1" style="6" min="16" max="16"/>
+    <col width="12" customWidth="1" style="6" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="23" t="inlineStr">
+      <c r="B1" s="24" t="inlineStr">
         <is>
           <t>싼타페 F/L 예상 가격 여론 주별 추이</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" s="25" t="inlineStr">
         <is>
           <t>{{conditions}}</t>
         </is>
@@ -1134,6 +1379,21 @@
       <c r="N3" s="16" t="inlineStr">
         <is>
           <t>평균 댓글수</t>
+        </is>
+      </c>
+      <c r="O3" s="16" t="inlineStr">
+        <is>
+          <t>가격 관련 댓글 수</t>
+        </is>
+      </c>
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t>댓글 부정·비난 비율</t>
+        </is>
+      </c>
+      <c r="Q3" s="16" t="inlineStr">
+        <is>
+          <t>댓글 인상액 평균(만 원)</t>
         </is>
       </c>
     </row>
@@ -1145,15 +1405,18 @@
       <c r="F4" s="22" t="n"/>
       <c r="G4" s="22" t="n"/>
       <c r="H4" s="22" t="n"/>
-      <c r="I4" s="27" t="n"/>
+      <c r="I4" s="28" t="n"/>
       <c r="J4" s="22" t="n"/>
       <c r="K4" s="22" t="n"/>
       <c r="L4" s="22" t="n"/>
       <c r="M4" s="22" t="n"/>
-      <c r="N4" s="28" t="n"/>
+      <c r="N4" s="29" t="n"/>
+      <c r="O4" s="22" t="n"/>
+      <c r="P4" s="28" t="n"/>
+      <c r="Q4" s="22" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="B3:N4"/>
+  <autoFilter ref="B3:Q4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader/>

--- a/price-extension/price-template.xlsx
+++ b/price-extension/price-template.xlsx
@@ -272,7 +272,7 @@
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="FF7030A0"/>
+        <color rgb="FFBF8F00"/>
       </font>
     </dxf>
     <dxf>
